--- a/data/numeric/input/old_data_69/焊机维修记录8月.xlsx
+++ b/data/numeric/input/old_data_69/焊机维修记录8月.xlsx
@@ -1629,13 +1629,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ED60942-A044-4030-B73B-9271CDFE3033}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{355576DA-3A44-425E-A5DD-9751C10B8264}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA1FEF4D-3D78-4D4F-8EDA-DF7ADAA14717}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{500C2FC9-2719-480C-BCED-ED1CD92A3A8A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A06B237-33B7-415C-B3BE-BBCB1D138C72}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E424102-0D72-4CC0-827C-3EFB376BC77B}"/>
 </file>